--- a/Configs/GameConfig/Datas/level_chest.xlsx
+++ b/Configs/GameConfig/Datas/level_chest.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18420" windowHeight="13410"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1232,8 +1232,38 @@
         <v>2003</v>
       </c>
     </row>
+    <row r="9" spans="1:20">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+      <c r="D10">
+        <v>2005</v>
+      </c>
+    </row>
     <row r="11" spans="1:20">
-      <c r="C11" s="5"/>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>2006</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="C13" s="5"/>
